--- a/Starfront/文档/配置表/UnitProductionResource.xlsx
+++ b/Starfront/文档/配置表/UnitProductionResource.xlsx
@@ -1284,132 +1284,147 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="7.5" customWidth="1"/>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.25" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="17.25" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" ht="17.25" spans="1:5">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5">
-        <v>1101</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1101</v>
-      </c>
-      <c r="D4" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="17.25" spans="1:5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5">
-        <v>1102</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1102</v>
-      </c>
-      <c r="D5" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="17.25" spans="1:5">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5">
-        <v>1103</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1103</v>
-      </c>
-      <c r="D6" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="17.25" spans="1:5">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5">
-        <v>1104</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1104</v>
-      </c>
-      <c r="D7" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:E7"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="8" customWidth="1"/>
+    <ns0:col min="2" max="2" width="7.5" customWidth="1"/>
+    <ns0:col min="3" max="3" width="11.625" customWidth="1"/>
+    <ns0:col min="4" max="4" width="18.25" customWidth="1"/>
+    <ns0:col min="5" max="5" width="13.75" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="17.25" spans="1:5">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="2" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="2" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="2" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="2" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" ht="17.25" spans="1:5">
+      <ns0:c r="A2" s="3" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="4" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="4" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="4" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="4" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" ht="17.25" spans="1:5">
+      <ns0:c r="A3" s="1" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="2" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="2" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="2" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="2" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4" ht="17.25" spans="1:5">
+      <ns0:c r="A4" s="5"/>
+      <ns0:c r="B4" s="5">
+        <ns0:v>1101</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" s="5">
+        <ns0:v>1101</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" s="5">
+        <ns0:v>10000</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="5">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5" ht="17.25" spans="1:5">
+      <ns0:c r="A5" s="5"/>
+      <ns0:c r="B5" s="5">
+        <ns0:v>1102</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="5">
+        <ns0:v>1102</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="5">
+        <ns0:v>10000</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="5">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6" ht="17.25" spans="1:5">
+      <ns0:c r="A6" s="5"/>
+      <ns0:c r="B6" s="5">
+        <ns0:v>1103</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="5">
+        <ns0:v>1103</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="5">
+        <ns0:v>10000</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="5">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7" ht="17.25" spans="1:5">
+      <ns0:c r="A7" s="5"/>
+      <ns0:c r="B7" s="5">
+        <ns0:v>1104</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="5">
+        <ns0:v>1104</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="5">
+        <ns0:v>10000</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="5">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8" ht="25" customHeight="1">
+      <ns0:c r="B8" t="n" s="5">
+        <ns0:v>1201</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" t="n" s="5">
+        <ns0:v>1201</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" t="n" s="5">
+        <ns0:v>15000</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" t="n" s="5">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:headerFooter/>
+  <ns0:legacyDrawing ns1:id="rId2"/>
+  <ns0:mergeCells count="0"/>
+</ns0:worksheet>
 </file>